--- a/BOM/PDU_Main_Connector_Board.xlsx
+++ b/BOM/PDU_Main_Connector_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\PDU_Main_Connector_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107B94D0-CAE7-47CC-9627-F15075007CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9DC7FB-9140-4D53-A5FB-F2AE63B83C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
